--- a/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
@@ -483,43 +483,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>P, T, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.951948776342316</v>
+        <v>0.9615427745718916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02869233852278334</v>
+        <v>0.0286816359599277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001855555433558486</v>
+        <v>0.00148507172493824</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04307615852833777</v>
+        <v>0.03853662835456989</v>
       </c>
       <c r="H2" t="n">
-        <v>167.0726924452773</v>
+        <v>410.5648076062061</v>
       </c>
       <c r="I2" t="n">
-        <v>-299.0577025374138</v>
+        <v>-320.639194830152</v>
       </c>
       <c r="J2" t="n">
-        <v>-271.7402904772738</v>
+        <v>-303.0780013629191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -527,101 +527,101 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>P, Xlag1_calc, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9514612393882063</v>
+        <v>0.9525618968370339</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0287055806676488</v>
+        <v>0.02891126629008585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001874382255757719</v>
+        <v>0.001831879052838098</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04329413650550983</v>
+        <v>0.04280045622231261</v>
       </c>
       <c r="H3" t="n">
-        <v>189.6658991510137</v>
+        <v>173.3541454442395</v>
       </c>
       <c r="I3" t="n">
-        <v>-300.5327591469164</v>
+        <v>-299.7254777733424</v>
       </c>
       <c r="J3" t="n">
-        <v>-275.1665908053579</v>
+        <v>-272.4080657132025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, mu, Plag1, X_calc, V_calc</t>
+          <t>P, mu, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9510860015023372</v>
+        <v>0.9514612393882063</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03166824804753914</v>
+        <v>0.0287055806676488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001888872515214203</v>
+        <v>0.001874382255757719</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0434611609970811</v>
+        <v>0.04329413650550983</v>
       </c>
       <c r="H4" t="n">
-        <v>207.4186581556484</v>
+        <v>189.6658991510137</v>
       </c>
       <c r="I4" t="n">
-        <v>-304.1323093972175</v>
+        <v>-298.5327591469164</v>
       </c>
       <c r="J4" t="n">
-        <v>-282.6686284928218</v>
+        <v>-271.2153470867764</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>P, mu, Plag1, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9510381682810218</v>
+        <v>0.9510859854913588</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02824910669854851</v>
+        <v>0.03166827505888317</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001890719652226752</v>
+        <v>0.001888873133497268</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04348240623777336</v>
+        <v>0.04346116811013331</v>
       </c>
       <c r="H5" t="n">
-        <v>176.543291708269</v>
+        <v>207.4188679957677</v>
       </c>
       <c r="I5" t="n">
-        <v>-298.0814832085472</v>
+        <v>-302.1322923761037</v>
       </c>
       <c r="J5" t="n">
-        <v>-270.7640711484073</v>
+        <v>-278.7173677531266</v>
       </c>
     </row>
     <row r="6">
@@ -667,33 +667,33 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V, P, X_calc</t>
+          <t>V, P, Plag1, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8359383001808718</v>
+        <v>0.8418802336547271</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06190146953764607</v>
+        <v>0.04600062779944737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006335438629137661</v>
+        <v>0.006105983766098139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0795954686470132</v>
+        <v>0.07814079450644291</v>
       </c>
       <c r="H7" t="n">
-        <v>1446.795457794906</v>
+        <v>566.4143900605686</v>
       </c>
       <c r="I7" t="n">
-        <v>-257.2030038869127</v>
+        <v>-257.1212742543704</v>
       </c>
       <c r="J7" t="n">
-        <v>-251.3492727311684</v>
+        <v>-249.3162993800447</v>
       </c>
     </row>
     <row r="8">
@@ -703,105 +703,105 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V, P, T, dVdt, Plag1, X_calc, V_calc, dVdt_calc</t>
+          <t>V, P, T, dVdt, Xlag1_calc, Plag1, X_calc, V_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7098119816121783</v>
+        <v>0.7134223470080454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04708345280397618</v>
+        <v>0.04626054382416241</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01120595716997907</v>
+        <v>0.01106653859501919</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1058581936837157</v>
+        <v>0.1051976168694861</v>
       </c>
       <c r="H8" t="n">
-        <v>203.5277266370254</v>
+        <v>194.044954273099</v>
       </c>
       <c r="I8" t="n">
-        <v>-217.548107099207</v>
+        <v>-216.1991217557679</v>
       </c>
       <c r="J8" t="n">
-        <v>-201.9381573505556</v>
+        <v>-198.6379282885351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, dXdt</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6620011808594183</v>
+        <v>0.6762786500457258</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0791737280967882</v>
+        <v>0.06675445865743511</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01305222838570449</v>
+        <v>0.01250088684828913</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1142463495508915</v>
+        <v>0.1118073649107657</v>
       </c>
       <c r="H9" t="n">
-        <v>1380.797599734351</v>
+        <v>693.0399206622502</v>
       </c>
       <c r="I9" t="n">
-        <v>-197.6174129178109</v>
+        <v>-195.8616958450265</v>
       </c>
       <c r="J9" t="n">
-        <v>-170.3000008576709</v>
+        <v>-164.6417963477236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V, P, Plag1, dXdt_calc</t>
+          <t>P, dXdt</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6404132810670857</v>
+        <v>0.6620011808594183</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06620670823468591</v>
+        <v>0.0791737280967882</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01388587093857989</v>
+        <v>0.01305222838570449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1178383254233524</v>
+        <v>0.1142463495508915</v>
       </c>
       <c r="H10" t="n">
-        <v>579.033520099252</v>
+        <v>1380.797599734351</v>
       </c>
       <c r="I10" t="n">
-        <v>-198.3979386225855</v>
+        <v>-195.6174129178109</v>
       </c>
       <c r="J10" t="n">
-        <v>-174.9830139996084</v>
+        <v>-166.3487571390895</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -495,25 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9615427745718916</v>
+        <v>0.9615289703283246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0286816359599277</v>
+        <v>0.02869025522313976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00148507172493824</v>
+        <v>0.001485604786298492</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03853662835456989</v>
+        <v>0.03854354402877986</v>
       </c>
       <c r="H2" t="n">
-        <v>410.5648076062061</v>
+        <v>15612450.50209574</v>
       </c>
       <c r="I2" t="n">
-        <v>-320.639194830152</v>
+        <v>0.01658123225191156</v>
       </c>
       <c r="J2" t="n">
-        <v>-303.0780013629191</v>
+        <v>-322.6205329590759</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-307.0105832104245</v>
       </c>
     </row>
     <row r="3">
@@ -523,33 +531,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Xlag1_calc, Plag1</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9525618968370339</v>
+        <v>0.9519458082951135</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02891126629008585</v>
+        <v>0.0286925303220087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001831879052838098</v>
+        <v>0.001855670040748763</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04280045622231261</v>
+        <v>0.04307748879343785</v>
       </c>
       <c r="H3" t="n">
-        <v>173.3541454442395</v>
+        <v>19401663.05465423</v>
       </c>
       <c r="I3" t="n">
-        <v>-299.7254777733424</v>
+        <v>0.01671522653999007</v>
       </c>
       <c r="J3" t="n">
-        <v>-272.4080657132025</v>
+        <v>-323.0544908899741</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-319.1520034528112</v>
       </c>
     </row>
     <row r="4">
@@ -567,25 +578,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9514612393882063</v>
+        <v>0.9514612375219347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0287055806676488</v>
+        <v>0.02870558089285108</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001874382255757719</v>
+        <v>0.001874382320250469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04329413650550983</v>
+        <v>0.04329413725033066</v>
       </c>
       <c r="H4" t="n">
-        <v>189.6658991510137</v>
+        <v>20737587.05991539</v>
       </c>
       <c r="I4" t="n">
-        <v>-298.5327591469164</v>
+        <v>0.01737369636759493</v>
       </c>
       <c r="J4" t="n">
-        <v>-271.2153470867764</v>
+        <v>-320.532757357728</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-314.6790262019837</v>
       </c>
     </row>
     <row r="5">
@@ -595,33 +609,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, mu, Plag1, X_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9510859854913588</v>
+        <v>0.9505245988685782</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03166827505888317</v>
+        <v>0.02843183481385724</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001888873133497268</v>
+        <v>0.00191055174119745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04346116811013331</v>
+        <v>0.04370985862705861</v>
       </c>
       <c r="H5" t="n">
-        <v>207.4188679957677</v>
+        <v>17062421.57044393</v>
       </c>
       <c r="I5" t="n">
-        <v>-302.1322923761037</v>
+        <v>0.01718000655826476</v>
       </c>
       <c r="J5" t="n">
-        <v>-278.7173677531266</v>
+        <v>-321.5388868628802</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-317.6363994257174</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.884792402551263</v>
+        <v>0.8849179223209453</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03474281591026388</v>
+        <v>0.03474230150330163</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004448879074467387</v>
+        <v>0.004444031960575623</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0666999180994054</v>
+        <v>0.06666357296586813</v>
       </c>
       <c r="H6" t="n">
-        <v>151.3623934977476</v>
+        <v>16041656.46431012</v>
       </c>
       <c r="I6" t="n">
-        <v>-277.5853616114536</v>
+        <v>0.03863544567611934</v>
       </c>
       <c r="J6" t="n">
-        <v>-273.6828741742908</v>
+        <v>-277.6420471998596</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-273.7395597626967</v>
       </c>
     </row>
     <row r="7">
@@ -667,33 +687,36 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V, P, Plag1, X_calc</t>
+          <t>V, P, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8418802336547271</v>
+        <v>0.8359421097742878</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04600062779944737</v>
+        <v>0.06184963973779968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006105983766098139</v>
+        <v>0.006335291491529675</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07814079450644291</v>
+        <v>0.0795945443578244</v>
       </c>
       <c r="H7" t="n">
-        <v>566.4143900605686</v>
+        <v>73023573.45764431</v>
       </c>
       <c r="I7" t="n">
-        <v>-257.1212742543704</v>
+        <v>0.05515207111178443</v>
       </c>
       <c r="J7" t="n">
-        <v>-249.3162993800447</v>
+        <v>-257.2042115766894</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-251.3504804209452</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +726,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V, P, T, dVdt, Xlag1_calc, Plag1, X_calc, V_calc, dVdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7134223470080454</v>
+        <v>0.7081952016029331</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04626054382416241</v>
+        <v>0.0654528835130066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01106653859501919</v>
+        <v>0.01126839101690907</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1051976168694861</v>
+        <v>0.1061526778602833</v>
       </c>
       <c r="H8" t="n">
-        <v>194.044954273099</v>
+        <v>38100689.78775699</v>
       </c>
       <c r="I8" t="n">
-        <v>-216.1991217557679</v>
+        <v>0.09592931323095642</v>
       </c>
       <c r="J8" t="n">
-        <v>-198.6379282885351</v>
+        <v>-231.2591938577664</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-229.307950139185</v>
       </c>
     </row>
     <row r="9">
@@ -747,25 +773,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6762786500457258</v>
+        <v>0.7013479840001846</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06675445865743511</v>
+        <v>0.06487062731702163</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01250088684828913</v>
+        <v>0.01153280450753525</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1118073649107657</v>
+        <v>0.107390895831701</v>
       </c>
       <c r="H9" t="n">
-        <v>693.0399206622502</v>
+        <v>36666594.3694059</v>
       </c>
       <c r="I9" t="n">
-        <v>-195.8616958450265</v>
+        <v>0.0981685679552193</v>
       </c>
       <c r="J9" t="n">
-        <v>-164.6417963477236</v>
+        <v>-230.0531064064518</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-228.1018626878704</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P, dXdt</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6620011808594183</v>
+        <v>0.6570386249473223</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0791737280967882</v>
+        <v>0.08128629488349531</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01305222838570449</v>
+        <v>0.01324386336009348</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1142463495508915</v>
+        <v>0.1150819853847399</v>
       </c>
       <c r="H10" t="n">
-        <v>1380.797599734351</v>
+        <v>57909277.78054834</v>
       </c>
       <c r="I10" t="n">
-        <v>-195.6174129178109</v>
+        <v>0.1126591168678688</v>
       </c>
       <c r="J10" t="n">
-        <v>-166.3487571390895</v>
+        <v>-222.8594907763379</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-220.9082470577565</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
@@ -488,46 +488,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, T, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9615289703283246</v>
+        <v>0.5263120635066294</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02869025522313976</v>
+        <v>0.08384619587453467</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001485604786298492</v>
+        <v>0.01829202583128858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03854354402877986</v>
+        <v>0.1352480159976056</v>
       </c>
       <c r="H2" t="n">
-        <v>15612450.50209574</v>
+        <v>217.7332833120806</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01658123225191156</v>
+        <v>0.1559107990299132</v>
       </c>
       <c r="J2" t="n">
-        <v>-322.6205329590759</v>
+        <v>-204.0670831732565</v>
       </c>
       <c r="K2" t="n">
-        <v>-307.0105832104245</v>
+        <v>-200.1645957360936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,77 +535,77 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9519458082951135</v>
+        <v>0.4443458169981793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0286925303220087</v>
+        <v>0.0719940335324048</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001855670040748763</v>
+        <v>0.0214572504083078</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04307748879343785</v>
+        <v>0.1464829355532848</v>
       </c>
       <c r="H3" t="n">
-        <v>19401663.05465423</v>
+        <v>215.570586334437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01671522653999007</v>
+        <v>0.1827163301863617</v>
       </c>
       <c r="J3" t="n">
-        <v>-323.0544908899741</v>
+        <v>-195.7680191701363</v>
       </c>
       <c r="K3" t="n">
-        <v>-319.1520034528112</v>
+        <v>-191.8655317329735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>X_calc, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9514612375219347</v>
+        <v>0.2947740153864838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02870558089285108</v>
+        <v>0.098361587556869</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001874382320250469</v>
+        <v>0.0272331442994789</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04329413725033066</v>
+        <v>0.1650246778499473</v>
       </c>
       <c r="H4" t="n">
-        <v>20737587.05991539</v>
+        <v>824.3934358044955</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01737369636759493</v>
+        <v>0.2316309963936901</v>
       </c>
       <c r="J4" t="n">
-        <v>-320.532757357728</v>
+        <v>-183.3726663679512</v>
       </c>
       <c r="K4" t="n">
-        <v>-314.6790262019837</v>
+        <v>-179.4701789307884</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,71 +613,71 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>X_calc, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9505245988685782</v>
+        <v>0.2673821731232106</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02843183481385724</v>
+        <v>0.08365180100947602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00191055174119745</v>
+        <v>0.028290913027886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04370985862705861</v>
+        <v>0.1681990280230121</v>
       </c>
       <c r="H5" t="n">
-        <v>17062421.57044393</v>
+        <v>389.7642240201361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01718000655826476</v>
+        <v>0.2405889871825571</v>
       </c>
       <c r="J5" t="n">
-        <v>-321.5388868628802</v>
+        <v>-181.3911602564209</v>
       </c>
       <c r="K5" t="n">
-        <v>-317.6363994257174</v>
+        <v>-177.488672819258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8849179223209453</v>
+        <v>0.1101839734731597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03474230150330163</v>
+        <v>0.102156825702162</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004444031960575623</v>
+        <v>0.03436130939456872</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06666357296586813</v>
+        <v>0.1853680376833307</v>
       </c>
       <c r="H6" t="n">
-        <v>16041656.46431012</v>
+        <v>503.5980905516895</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03863544567611934</v>
+        <v>0.2934977245342503</v>
       </c>
       <c r="J6" t="n">
-        <v>-277.6420471998596</v>
+        <v>-165.2828518732108</v>
       </c>
       <c r="K6" t="n">
-        <v>-273.7395597626967</v>
+        <v>-155.5266332803037</v>
       </c>
     </row>
     <row r="7">
@@ -687,42 +687,42 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V, P, X_calc</t>
+          <t>T, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8359421097742878</v>
+        <v>0.0894056235212819</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06184963973779968</v>
+        <v>0.09620722790374076</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006335291491529675</v>
+        <v>0.03516369021276087</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0795945443578244</v>
+        <v>0.1875198395177451</v>
       </c>
       <c r="H7" t="n">
-        <v>73023573.45764431</v>
+        <v>1136.459579687785</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05515207111178443</v>
+        <v>0.2987928960925481</v>
       </c>
       <c r="J7" t="n">
-        <v>-257.2042115766894</v>
+        <v>-170.0825453544245</v>
       </c>
       <c r="K7" t="n">
-        <v>-251.3504804209452</v>
+        <v>-166.1800579172617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -730,38 +730,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>dVdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7081952016029331</v>
+        <v>-0.1221702224341794</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0654528835130066</v>
+        <v>0.1145371341163558</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01126839101690907</v>
+        <v>0.04333394438504164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1061526778602833</v>
+        <v>0.2081680676401682</v>
       </c>
       <c r="H8" t="n">
-        <v>38100689.78775699</v>
+        <v>1469.889582688008</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09592931323095642</v>
+        <v>0.7349696555995661</v>
       </c>
       <c r="J8" t="n">
-        <v>-231.2591938577664</v>
+        <v>-161.2185888372425</v>
       </c>
       <c r="K8" t="n">
-        <v>-229.307950139185</v>
+        <v>-159.267345118661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,71 +769,71 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7013479840001846</v>
+        <v>-0.1482752905753759</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06487062731702163</v>
+        <v>0.1189218230589453</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01153280450753525</v>
+        <v>0.04434202279274033</v>
       </c>
       <c r="G9" t="n">
-        <v>0.107390895831701</v>
+        <v>0.2105754562923712</v>
       </c>
       <c r="H9" t="n">
-        <v>36666594.3694059</v>
+        <v>1603.920303065977</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0981685679552193</v>
+        <v>0.7520440062550621</v>
       </c>
       <c r="J9" t="n">
-        <v>-230.0531064064518</v>
+        <v>-160.0227677011202</v>
       </c>
       <c r="K9" t="n">
-        <v>-228.1018626878704</v>
+        <v>-158.0715239825388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6570386249473223</v>
+        <v>-0.3568948629746951</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08128629488349531</v>
+        <v>0.1111941558073416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01324386336009348</v>
+        <v>0.05239811692823903</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1150819853847399</v>
+        <v>0.2289063496896472</v>
       </c>
       <c r="H10" t="n">
-        <v>57909277.78054834</v>
+        <v>1028.299162075215</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1126591168678688</v>
+        <v>0.8894942814843517</v>
       </c>
       <c r="J10" t="n">
-        <v>-222.8594907763379</v>
+        <v>-149.3420004888127</v>
       </c>
       <c r="K10" t="n">
-        <v>-220.9082470577565</v>
+        <v>-145.4395130516498</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -500,34 +500,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5263120635066294</v>
+        <v>0.5925503645483179</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08384619587453467</v>
+        <v>0.07010934121903095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01829202583128858</v>
+        <v>0.01516465195151283</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1352480159976056</v>
+        <v>0.1231448413516085</v>
       </c>
       <c r="H2" t="n">
-        <v>217.7332833120806</v>
+        <v>242.3391609977237</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1559107990299132</v>
+        <v>0.1338501470015636</v>
       </c>
       <c r="J2" t="n">
-        <v>-204.0670831732565</v>
+        <v>-222.1945567994622</v>
       </c>
       <c r="K2" t="n">
-        <v>-200.1645957360936</v>
+        <v>-218.2165887063337</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4443458169981793</v>
+        <v>0.5187627830403984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0719940335324048</v>
+        <v>0.0816585682574285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0214572504083078</v>
+        <v>0.01791091282537776</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1464829355532848</v>
+        <v>0.1338316585318204</v>
       </c>
       <c r="H3" t="n">
-        <v>215.570586334437</v>
+        <v>193.0898721199998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1827163301863617</v>
+        <v>0.1579088040656449</v>
       </c>
       <c r="J3" t="n">
-        <v>-195.7680191701363</v>
+        <v>-213.2066352299288</v>
       </c>
       <c r="K3" t="n">
-        <v>-191.8655317329735</v>
+        <v>-209.2286671368002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,38 +574,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X_calc, V_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2947740153864838</v>
+        <v>0.4411561863058815</v>
       </c>
       <c r="E4" t="n">
-        <v>0.098361587556869</v>
+        <v>0.0714108938107039</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0272331442994789</v>
+        <v>0.02079931160211423</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1650246778499473</v>
+        <v>0.1442196644085481</v>
       </c>
       <c r="H4" t="n">
-        <v>824.3934358044955</v>
+        <v>209.0415627377951</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2316309963936901</v>
+        <v>0.1832126622297155</v>
       </c>
       <c r="J4" t="n">
-        <v>-183.3726663679512</v>
+        <v>-205.1331109992366</v>
       </c>
       <c r="K4" t="n">
-        <v>-179.4701789307884</v>
+        <v>-201.155142906108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,110 +613,110 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>X_calc, V_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2673821731232106</v>
+        <v>0.3164295144964755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08365180100947602</v>
+        <v>0.08730476527784481</v>
       </c>
       <c r="F5" t="n">
-        <v>0.028290913027886</v>
+        <v>0.02544144746993368</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1681990280230121</v>
+        <v>0.1595037537800715</v>
       </c>
       <c r="H5" t="n">
-        <v>389.7642240201361</v>
+        <v>699.3741113189545</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2405889871825571</v>
+        <v>0.2238801588800109</v>
       </c>
       <c r="J5" t="n">
-        <v>-181.3911602564209</v>
+        <v>-194.2542848151909</v>
       </c>
       <c r="K5" t="n">
-        <v>-177.488672819258</v>
+        <v>-190.2763167220624</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>X_calc, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1101839734731597</v>
+        <v>0.2708356441322819</v>
       </c>
       <c r="E6" t="n">
-        <v>0.102156825702162</v>
+        <v>0.08111788935741319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03436130939456872</v>
+        <v>0.02713838155708513</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1853680376833307</v>
+        <v>0.1647373107619677</v>
       </c>
       <c r="H6" t="n">
-        <v>503.5980905516895</v>
+        <v>389.3078886976312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2934977245342503</v>
+        <v>0.2387461738502751</v>
       </c>
       <c r="J6" t="n">
-        <v>-165.2828518732108</v>
+        <v>-190.7675380116469</v>
       </c>
       <c r="K6" t="n">
-        <v>-155.5266332803037</v>
+        <v>-186.7895699185183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, V_calc</t>
+          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0894056235212819</v>
+        <v>0.184941294839144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09620722790374076</v>
+        <v>0.09685166472575378</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03516369021276087</v>
+        <v>0.03033523780212299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1875198395177451</v>
+        <v>0.1741701403861264</v>
       </c>
       <c r="H7" t="n">
-        <v>1136.459579687785</v>
+        <v>487.0318988094806</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2987928960925481</v>
+        <v>0.2682522780097429</v>
       </c>
       <c r="J7" t="n">
-        <v>-170.0825453544245</v>
+        <v>-178.7540450346206</v>
       </c>
       <c r="K7" t="n">
-        <v>-166.1800579172617</v>
+        <v>-168.8091248017992</v>
       </c>
     </row>
     <row r="8">
@@ -726,36 +726,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dVdt_calc</t>
+          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1221702224341794</v>
+        <v>0.05379995666117654</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1145371341163558</v>
+        <v>0.1110149885519101</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04333394438504164</v>
+        <v>0.03521611773644889</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2081680676401682</v>
+        <v>0.18765957938898</v>
       </c>
       <c r="H8" t="n">
-        <v>1469.889582688008</v>
+        <v>512.5776817549606</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7349696555995661</v>
+        <v>0.3105112954171613</v>
       </c>
       <c r="J8" t="n">
-        <v>-161.2185888372425</v>
+        <v>-172.6975761906415</v>
       </c>
       <c r="K8" t="n">
-        <v>-159.267345118661</v>
+        <v>-164.7416400043844</v>
       </c>
     </row>
     <row r="9">
@@ -773,28 +773,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1482752905753759</v>
+        <v>-0.1467699911066715</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1189218230589453</v>
+        <v>0.1161582194401391</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04434202279274033</v>
+        <v>0.0426810242799552</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2105754562923712</v>
+        <v>0.2065938631226862</v>
       </c>
       <c r="H9" t="n">
-        <v>1603.920303065977</v>
+        <v>1523.010079257802</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7520440062550621</v>
+        <v>0.7488154286559404</v>
       </c>
       <c r="J9" t="n">
-        <v>-160.0227677011202</v>
+        <v>-168.3160461038399</v>
       </c>
       <c r="K9" t="n">
-        <v>-158.0715239825388</v>
+        <v>-166.3270620572757</v>
       </c>
     </row>
     <row r="10">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T, mu_calc</t>
+          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3568948629746951</v>
+        <v>-0.2167231015709059</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1111941558073416</v>
+        <v>0.1040500040169121</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05239811692823903</v>
+        <v>0.04528457200908709</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2289063496896472</v>
+        <v>0.2128017199392127</v>
       </c>
       <c r="H10" t="n">
-        <v>1028.299162075215</v>
+        <v>566.9100245615045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8894942814843517</v>
+        <v>0.7984322617552656</v>
       </c>
       <c r="J10" t="n">
-        <v>-149.3420004888127</v>
+        <v>-157.1185994256294</v>
       </c>
       <c r="K10" t="n">
-        <v>-145.4395130516498</v>
+        <v>-147.173679192808</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP/metrics_global.xlsx
@@ -488,85 +488,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1, dXdt_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5925503645483179</v>
+        <v>0.9538430565709496</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07010934121903095</v>
+        <v>0.02821616164604792</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01516465195151283</v>
+        <v>0.001782405538438981</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1231448413516085</v>
+        <v>0.04221854495880905</v>
       </c>
       <c r="H2" t="n">
-        <v>242.3391609977237</v>
+        <v>160.045323505615</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1338501470015636</v>
+        <v>0.01659476690562241</v>
       </c>
       <c r="J2" t="n">
-        <v>-222.1945567994622</v>
+        <v>-323.149152849045</v>
       </c>
       <c r="K2" t="n">
-        <v>-218.2165887063337</v>
+        <v>-317.2954216933007</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1, mu_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5187627830403984</v>
+        <v>0.952970663360927</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0816585682574285</v>
+        <v>0.02829880402016886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01791091282537776</v>
+        <v>0.001816094044950055</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1338316585318204</v>
+        <v>0.04261565492809016</v>
       </c>
       <c r="H3" t="n">
-        <v>193.0898721199998</v>
+        <v>165.9410315922835</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1579088040656449</v>
+        <v>0.01688006682318696</v>
       </c>
       <c r="J3" t="n">
-        <v>-213.2066352299288</v>
+        <v>-322.1754950904123</v>
       </c>
       <c r="K3" t="n">
-        <v>-209.2286671368002</v>
+        <v>-316.321763934668</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,38 +574,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4411561863058815</v>
+        <v>0.9505246001779236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0714108938107039</v>
+        <v>0.02843183447573834</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02079931160211423</v>
+        <v>0.001910551698357251</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1442196644085481</v>
+        <v>0.04370985813700669</v>
       </c>
       <c r="H4" t="n">
-        <v>209.0415627377951</v>
+        <v>172.7358511455645</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1832126622297155</v>
+        <v>0.01718000613547299</v>
       </c>
       <c r="J4" t="n">
-        <v>-205.1331109992366</v>
+        <v>-321.5388880288734</v>
       </c>
       <c r="K4" t="n">
-        <v>-201.155142906108</v>
+        <v>-317.6364005917106</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,38 +613,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3164295144964755</v>
+        <v>0.9495023800128063</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08730476527784481</v>
+        <v>0.02873973753795243</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02544144746993368</v>
+        <v>0.001950025951816209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1595037537800715</v>
+        <v>0.04415909817711645</v>
       </c>
       <c r="H5" t="n">
-        <v>699.3741113189545</v>
+        <v>167.4283116732778</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2238801588800109</v>
+        <v>0.01751430416242946</v>
       </c>
       <c r="J5" t="n">
-        <v>-194.2542848151909</v>
+        <v>-320.4754550893099</v>
       </c>
       <c r="K5" t="n">
-        <v>-190.2763167220624</v>
+        <v>-316.572967652147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,116 +652,116 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2708356441322819</v>
+        <v>0.884792402551263</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08111788935741319</v>
+        <v>0.03474281591026388</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02713838155708513</v>
+        <v>0.004448879074467387</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1647373107619677</v>
+        <v>0.0666999180994054</v>
       </c>
       <c r="H6" t="n">
-        <v>389.3078886976312</v>
+        <v>151.3623934977476</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2387461738502751</v>
+        <v>0.03867649458674827</v>
       </c>
       <c r="J6" t="n">
-        <v>-190.7675380116469</v>
+        <v>-277.5853616114536</v>
       </c>
       <c r="K6" t="n">
-        <v>-186.7895699185183</v>
+        <v>-273.6828741742908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.184941294839144</v>
+        <v>0.7662116478375927</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09685166472575378</v>
+        <v>0.05408327901705222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03033523780212299</v>
+        <v>0.009028016648401593</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1741701403861264</v>
+        <v>0.09501587577032373</v>
       </c>
       <c r="H7" t="n">
-        <v>487.0318988094806</v>
+        <v>416.8862193412594</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2682522780097429</v>
+        <v>0.07745611730260334</v>
       </c>
       <c r="J7" t="n">
-        <v>-178.7540450346206</v>
+        <v>-240.7859739490518</v>
       </c>
       <c r="K7" t="n">
-        <v>-168.8091248017992</v>
+        <v>-236.8834865118889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05379995666117654</v>
+        <v>0.7449721479274842</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1110149885519101</v>
+        <v>0.05536792496150245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03521611773644889</v>
+        <v>0.009848205323408715</v>
       </c>
       <c r="G8" t="n">
-        <v>0.18765957938898</v>
+        <v>0.09923812434447114</v>
       </c>
       <c r="H8" t="n">
-        <v>512.5776817549606</v>
+        <v>216.9121338252996</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3105112954171613</v>
+        <v>0.08440209934814084</v>
       </c>
       <c r="J8" t="n">
-        <v>-172.6975761906415</v>
+        <v>-236.2642341355289</v>
       </c>
       <c r="K8" t="n">
-        <v>-164.7416400043844</v>
+        <v>-232.3617466983661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,71 +769,71 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1467699911066715</v>
+        <v>0.7013479835425864</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1161582194401391</v>
+        <v>0.06487062800451482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0426810242799552</v>
+        <v>0.01153280457181726</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2065938631226862</v>
+        <v>0.1073908961309908</v>
       </c>
       <c r="H9" t="n">
-        <v>1523.010079257802</v>
+        <v>670.3608601335237</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7488154286559404</v>
+        <v>0.09816856813749616</v>
       </c>
       <c r="J9" t="n">
-        <v>-168.3160461038399</v>
+        <v>-230.0531061166121</v>
       </c>
       <c r="K9" t="n">
-        <v>-166.3270620572757</v>
+        <v>-228.1018623980307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2167231015709059</v>
+        <v>0.6570386264988707</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1040500040169121</v>
+        <v>0.08128629530844264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04528457200908709</v>
+        <v>0.01324386335370537</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2128017199392127</v>
+        <v>0.1150819853569853</v>
       </c>
       <c r="H10" t="n">
-        <v>566.9100245615045</v>
+        <v>1467.9362164118</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7984322617552656</v>
+        <v>0.1126591163979326</v>
       </c>
       <c r="J10" t="n">
-        <v>-157.1185994256294</v>
+        <v>-222.8594908014198</v>
       </c>
       <c r="K10" t="n">
-        <v>-147.173679192808</v>
+        <v>-220.9082470828384</v>
       </c>
     </row>
   </sheetData>
